--- a/Codelist Excel Files and Conversion Templates to XML/riInstallationMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/riInstallationMethod.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes classifying how the ground is handled as a rigid inclusion is formed - whether the technique displaces soil laterally, removes it, or does some of each. The technical report calls this the primary classifier, because the families produce different as-built records: a displacement technique generates no spoil and densifies the surrounding ground, a replacement technique removes soil. Used for the value of diggs:RIColumnType/riInstallationMethod (as-built), diggs:RIColumnSpecificationType/riInstallationMethod (specified) and diggs:RIConstructionActivityType/riInstallationMethod (as recorded by the activity). Orthogonal to columnType, which names the technique rather than what it does to the ground; each columnType entry declares which of these families it is compatible with, so the two cannot contradict each other. Named with the ri prefix because installation method is a concept other DIGGS domains will want under their own vocabularies.</t>
+          <t>Codes classifying how the ground is handled as a rigid inclusion is formed - whether the technique displaces soil laterally, removes it, or does some of each. The technical report calls this the primary classifier, because the families produce different as-built records: a displacement technique generates no spoil and densifies the surrounding ground, a replacement technique removes soil. Used for the value of diggs:RIColumnType/riInstallationMethod (as-built), diggs:RIColumnSpecificationType/riInstallationMethod (specified) and diggs:RIColumnConstructionType/riInstallationMethod (as recorded by the activity). Orthogonal to columnType, which names the technique rather than what it does to the ground; each columnType entry declares which of these families it is compatible with, so the two cannot contradict each other. Named with the ri prefix because installation method is a concept other DIGGS domains will want under their own vocabularies.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RIConstructionActivity/diggs:riInstallationMethod</t>
+          <t>//diggs:RIColumnConstruction/diggs:riInstallationMethod</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>//diggs:RIConstructionActivity/diggs:riInstallationMethod</t>
+          <t>//diggs:RIColumnConstruction/diggs:riInstallationMethod</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>//diggs:RIConstructionActivity/diggs:riInstallationMethod</t>
+          <t>//diggs:RIColumnConstruction/diggs:riInstallationMethod</t>
         </is>
       </c>
     </row>
